--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -56,11 +57,11 @@
   <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.7109375" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
     <col min="8" max="8" width="14.7109375" customWidth="true"/>
@@ -599,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="0">
-        <v>0</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="15">
@@ -613,16 +614,16 @@
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>0</v>
+        <v>0.0072127521457937766</v>
       </c>
       <c r="E15" s="0">
-        <v>0</v>
+        <v>0.0029833825591455651</v>
       </c>
       <c r="F15" s="0">
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>0</v>
+        <v>0.020116676725005066</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -642,31 +643,31 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0</v>
+        <v>0.0049227133996258693</v>
       </c>
       <c r="B16" s="0">
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>0</v>
+        <v>0.011412774699146568</v>
       </c>
       <c r="D16" s="0">
-        <v>0</v>
+        <v>0.012021253576322928</v>
       </c>
       <c r="E16" s="0">
-        <v>0</v>
+        <v>0.011336853724753116</v>
       </c>
       <c r="F16" s="0">
-        <v>0</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G16" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H16" s="0">
-        <v>0</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I16" s="0">
-        <v>0</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J16" s="0">
         <v>0</v>
@@ -675,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>0</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="17">
@@ -686,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0</v>
+        <v>0.020289377242927231</v>
       </c>
       <c r="D17" s="0">
-        <v>0</v>
+        <v>0.045680763590027124</v>
       </c>
       <c r="E17" s="0">
-        <v>0</v>
+        <v>0.026850443032310007</v>
       </c>
       <c r="F17" s="0">
-        <v>0</v>
+        <v>0.01455445184295745</v>
       </c>
       <c r="G17" s="0">
-        <v>0</v>
+        <v>0.12070006035003007</v>
       </c>
       <c r="H17" s="0">
-        <v>0</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I17" s="0">
-        <v>0</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J17" s="0">
         <v>0</v>
@@ -713,3052 +714,3052 @@
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>0</v>
+        <v>0.0093303890772245112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0</v>
+        <v>0.0049227133996258832</v>
       </c>
       <c r="B18" s="0">
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>0.090034111515489845</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>0.13944654148534635</v>
       </c>
       <c r="E18" s="0">
-        <v>0</v>
+        <v>0.058474298159253077</v>
       </c>
       <c r="F18" s="0">
-        <v>0</v>
+        <v>0.080049485136266196</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>0.28163347415007095</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>0.079531897971936757</v>
       </c>
       <c r="I18" s="0">
-        <v>0</v>
+        <v>0.015888462989811551</v>
       </c>
       <c r="J18" s="0">
-        <v>0</v>
+        <v>0.036805299963194767</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>0</v>
+        <v>0.013995583615836808</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0</v>
+        <v>0.017229496898690543</v>
       </c>
       <c r="B19" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>0.16992353440951558</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>0.36544610872021699</v>
       </c>
       <c r="E19" s="0">
-        <v>0</v>
+        <v>0.14916912795727783</v>
       </c>
       <c r="F19" s="0">
-        <v>0</v>
+        <v>0.11825492122402931</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>0.40233353450010018</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>0.10793614724762815</v>
       </c>
       <c r="I19" s="0">
-        <v>0</v>
+        <v>0.047665388969434529</v>
       </c>
       <c r="J19" s="0">
-        <v>0</v>
+        <v>0.11041589988958402</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>0.046651945386122565</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0</v>
+        <v>0.049227133996258693</v>
       </c>
       <c r="B20" s="0">
         <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0</v>
+        <v>0.32589812196451867</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>0.69482845671146532</v>
       </c>
       <c r="E20" s="0">
-        <v>0</v>
+        <v>0.29833825591455565</v>
       </c>
       <c r="F20" s="0">
-        <v>0</v>
+        <v>0.34202961830950013</v>
       </c>
       <c r="G20" s="0">
-        <v>0</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>0.24427654377094793</v>
       </c>
       <c r="I20" s="0">
-        <v>0</v>
+        <v>0.09334472006514262</v>
       </c>
       <c r="J20" s="0">
-        <v>0</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K20" s="0">
-        <v>0</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L20" s="0">
-        <v>0</v>
+        <v>0.11973999315771458</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0</v>
+        <v>0.18706310918578356</v>
       </c>
       <c r="B21" s="0">
-        <v>0</v>
+        <v>0.70175438596491357</v>
       </c>
       <c r="C21" s="0">
-        <v>0</v>
+        <v>0.61121748944318455</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>1.315125141249732</v>
       </c>
       <c r="E21" s="0">
-        <v>0</v>
+        <v>0.57698618693875226</v>
       </c>
       <c r="F21" s="0">
-        <v>0</v>
+        <v>0.62766073572754177</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>1.6898008449004258</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>0.64761688348577062</v>
       </c>
       <c r="I21" s="0">
-        <v>0</v>
+        <v>0.25818752358443775</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>0.62569009937431108</v>
       </c>
       <c r="K21" s="0">
-        <v>0</v>
+        <v>1.675257731958766</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>0.27680154262432794</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0</v>
+        <v>0.3618194348725014</v>
       </c>
       <c r="B22" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C22" s="0">
-        <v>0</v>
+        <v>1.1209880926717295</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>2.2071021566128897</v>
       </c>
       <c r="E22" s="0">
-        <v>0</v>
+        <v>1.0417971896536285</v>
       </c>
       <c r="F22" s="0">
-        <v>0</v>
+        <v>1.1752719863188144</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>2.8565680949507115</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>1.0964040220416964</v>
       </c>
       <c r="I22" s="0">
-        <v>0</v>
+        <v>0.47268177394689243</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K22" s="0">
-        <v>0</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L22" s="0">
-        <v>0</v>
+        <v>0.51472646409355227</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0</v>
+        <v>0.73348429654425451</v>
       </c>
       <c r="B23" s="0">
-        <v>0</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>1.8057545746205235</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>3.2000577020171637</v>
       </c>
       <c r="E23" s="0">
-        <v>0</v>
+        <v>1.6772576747516319</v>
       </c>
       <c r="F23" s="0">
-        <v>0</v>
+        <v>1.7247025433904579</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>3.6210018105009021</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>1.7553826052377421</v>
       </c>
       <c r="I23" s="0">
-        <v>0</v>
+        <v>1.0049452841055779</v>
       </c>
       <c r="J23" s="0">
-        <v>0</v>
+        <v>1.545822598454176</v>
       </c>
       <c r="K23" s="0">
-        <v>0</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L23" s="0">
-        <v>0</v>
+        <v>0.91904332410661449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0</v>
+        <v>1.0706901644186295</v>
       </c>
       <c r="B24" s="0">
-        <v>0</v>
+        <v>2.4561403508771975</v>
       </c>
       <c r="C24" s="0">
-        <v>0</v>
+        <v>2.5488530161427403</v>
       </c>
       <c r="D24" s="0">
-        <v>0</v>
+        <v>4.3420767917678535</v>
       </c>
       <c r="E24" s="0">
-        <v>0</v>
+        <v>2.2417136549419774</v>
       </c>
       <c r="F24" s="0">
-        <v>0</v>
+        <v>2.499727104027949</v>
       </c>
       <c r="G24" s="0">
-        <v>0</v>
+        <v>3.9629853148259984</v>
       </c>
       <c r="H24" s="0">
-        <v>0</v>
+        <v>2.6529568823496041</v>
       </c>
       <c r="I24" s="0">
-        <v>0</v>
+        <v>1.614665051339599</v>
       </c>
       <c r="J24" s="0">
-        <v>0</v>
+        <v>2.4843577475156469</v>
       </c>
       <c r="K24" s="0">
-        <v>0</v>
+        <v>5.9278350515464027</v>
       </c>
       <c r="L24" s="0">
-        <v>0</v>
+        <v>1.5597300407427019</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0</v>
+        <v>1.8017131042630681</v>
       </c>
       <c r="B25" s="0">
-        <v>0</v>
+        <v>3.7719298245614001</v>
       </c>
       <c r="C25" s="0">
-        <v>0</v>
+        <v>3.4251004958216531</v>
       </c>
       <c r="D25" s="0">
-        <v>0</v>
+        <v>5.2797345707210299</v>
       </c>
       <c r="E25" s="0">
-        <v>0</v>
+        <v>2.9087979951669176</v>
       </c>
       <c r="F25" s="0">
-        <v>0</v>
+        <v>3.2092566313721185</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>4.8883524441762178</v>
       </c>
       <c r="H25" s="0">
-        <v>0</v>
+        <v>3.5050843606203457</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>2.3336180016285657</v>
       </c>
       <c r="J25" s="0">
-        <v>0</v>
+        <v>3.7909458962090508</v>
       </c>
       <c r="K25" s="0">
-        <v>0</v>
+        <v>6.7010309278350455</v>
       </c>
       <c r="L25" s="0">
-        <v>0</v>
+        <v>2.3232668802289034</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0</v>
+        <v>2.3604410751206046</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>6.4035087719298192</v>
       </c>
       <c r="C26" s="0">
-        <v>0</v>
+        <v>4.0845052562167883</v>
       </c>
       <c r="D26" s="0">
-        <v>0</v>
+        <v>5.7485634601976248</v>
       </c>
       <c r="E26" s="0">
-        <v>0</v>
+        <v>3.4255198544109282</v>
       </c>
       <c r="F26" s="0">
-        <v>0</v>
+        <v>3.9333406105592514</v>
       </c>
       <c r="G26" s="0">
-        <v>0</v>
+        <v>4.9487024743512329</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>4.0220416974379329</v>
       </c>
       <c r="I26" s="0">
-        <v>0</v>
+        <v>3.3067863597545202</v>
       </c>
       <c r="J26" s="0">
-        <v>0</v>
+        <v>4.6926757453073202</v>
       </c>
       <c r="K26" s="0">
-        <v>0</v>
+        <v>9.6649484536082397</v>
       </c>
       <c r="L26" s="0">
-        <v>0</v>
+        <v>3.1645569620253138</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0</v>
+        <v>3.1751501427586857</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>6.6666666666666608</v>
       </c>
       <c r="C27" s="0">
-        <v>0</v>
+        <v>4.5930077733676526</v>
       </c>
       <c r="D27" s="0">
-        <v>0</v>
+        <v>5.7028826966075972</v>
       </c>
       <c r="E27" s="0">
-        <v>0</v>
+        <v>3.7560786419642556</v>
       </c>
       <c r="F27" s="0">
-        <v>0</v>
+        <v>4.3845286176909317</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>4.9487024743512329</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>4.4253820371527537</v>
       </c>
       <c r="I27" s="0">
-        <v>0</v>
+        <v>4.0038926734325004</v>
       </c>
       <c r="J27" s="0">
-        <v>0</v>
+        <v>4.8398969451600982</v>
       </c>
       <c r="K27" s="0">
-        <v>0</v>
+        <v>10.438144329896899</v>
       </c>
       <c r="L27" s="0">
-        <v>0</v>
+        <v>3.8690013373557646</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0</v>
+        <v>3.5148173673328706</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>7.2807017543859587</v>
       </c>
       <c r="C28" s="0">
-        <v>0</v>
+        <v>4.5663779657363106</v>
       </c>
       <c r="D28" s="0">
-        <v>0</v>
+        <v>5.6043084172817492</v>
       </c>
       <c r="E28" s="0">
-        <v>0.0029833825591455568</v>
+        <v>3.9076344759688499</v>
       </c>
       <c r="F28" s="0">
-        <v>0</v>
+        <v>4.2662736964669028</v>
       </c>
       <c r="G28" s="0">
-        <v>0</v>
+        <v>4.2848521424260673</v>
       </c>
       <c r="H28" s="0">
-        <v>0</v>
+        <v>4.5105947849798289</v>
       </c>
       <c r="I28" s="0">
-        <v>0.0039721157474528774</v>
+        <v>4.4388393477785906</v>
       </c>
       <c r="J28" s="0">
-        <v>0</v>
+        <v>4.950312845049683</v>
       </c>
       <c r="K28" s="0">
-        <v>0</v>
+        <v>9.5360824742267951</v>
       </c>
       <c r="L28" s="0">
-        <v>0</v>
+        <v>4.2997542997542961</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0</v>
+        <v>3.9012503692035234</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>6.4035087719298547</v>
       </c>
       <c r="C29" s="0">
-        <v>0</v>
+        <v>4.4560544769779176</v>
       </c>
       <c r="D29" s="0">
-        <v>0</v>
+        <v>4.5247998461279755</v>
       </c>
       <c r="E29" s="0">
-        <v>0.0047734120946329173</v>
+        <v>3.9291148303947203</v>
       </c>
       <c r="F29" s="0">
-        <v>0</v>
+        <v>4.2226103409380542</v>
       </c>
       <c r="G29" s="0">
-        <v>0</v>
+        <v>2.9370348018507477</v>
       </c>
       <c r="H29" s="0">
-        <v>0.0056808498551383551</v>
+        <v>3.9481906493211572</v>
       </c>
       <c r="I29" s="0">
-        <v>0.0019860578737264495</v>
+        <v>4.9115211217255102</v>
       </c>
       <c r="J29" s="0">
-        <v>0</v>
+        <v>4.6006624953993587</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>9.0206185567010735</v>
       </c>
       <c r="L29" s="0">
-        <v>0</v>
+        <v>4.3246353372935848</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0049227133996258693</v>
+        <v>3.7954120311115456</v>
       </c>
       <c r="B30" s="0">
-        <v>0.087719298245613961</v>
+        <v>6.7543859649122746</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0088766025437806654</v>
+        <v>4.4294246693465516</v>
       </c>
       <c r="D30" s="0">
-        <v>0.002404250715264586</v>
+        <v>3.7265886086601081</v>
       </c>
       <c r="E30" s="0">
-        <v>0.013723559772069561</v>
+        <v>3.8223097347772872</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0018193064803696812</v>
+        <v>3.9260633846377728</v>
       </c>
       <c r="G30" s="0">
-        <v>0</v>
+        <v>2.8766847716757167</v>
       </c>
       <c r="H30" s="0">
-        <v>0</v>
+        <v>3.7323183548258783</v>
       </c>
       <c r="I30" s="0">
-        <v>0.0059581736211793161</v>
+        <v>4.9333677583364732</v>
       </c>
       <c r="J30" s="0">
-        <v>0</v>
+        <v>4.1405962458593999</v>
       </c>
       <c r="K30" s="0">
-        <v>0</v>
+        <v>8.376288659793806</v>
       </c>
       <c r="L30" s="0">
-        <v>0.0031101296924081708</v>
+        <v>4.2344415762137242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0</v>
+        <v>3.6009648518263231</v>
       </c>
       <c r="B31" s="0">
-        <v>0.087719298245613961</v>
+        <v>4.6491228070175392</v>
       </c>
       <c r="C31" s="0">
-        <v>0.020289377242927231</v>
+        <v>4.0908456866052028</v>
       </c>
       <c r="D31" s="0">
-        <v>0.012021253576322928</v>
+        <v>3.3683552520856845</v>
       </c>
       <c r="E31" s="0">
-        <v>0.042960708851696013</v>
+        <v>3.6504668993705027</v>
       </c>
       <c r="F31" s="0">
-        <v>0.0036386129607393625</v>
+        <v>3.7750609467670895</v>
       </c>
       <c r="G31" s="0">
-        <v>0.020116676725005011</v>
+        <v>2.2933011466505713</v>
       </c>
       <c r="H31" s="0">
-        <v>0.051127648696244914</v>
+        <v>3.0449355223541414</v>
       </c>
       <c r="I31" s="0">
-        <v>0.047665388969434529</v>
+        <v>4.5997100355504319</v>
       </c>
       <c r="J31" s="0">
-        <v>0</v>
+        <v>3.8461538461538432</v>
       </c>
       <c r="K31" s="0">
-        <v>0</v>
+        <v>8.1185567010309203</v>
       </c>
       <c r="L31" s="0">
-        <v>0.0046651945386122556</v>
+        <v>3.9918514602058868</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.014768140198877608</v>
+        <v>3.7978733878113582</v>
       </c>
       <c r="B32" s="0">
-        <v>0.35087719298245584</v>
+        <v>3.5964912280701724</v>
       </c>
       <c r="C32" s="0">
-        <v>0.077353250738660076</v>
+        <v>3.9361391851278826</v>
       </c>
       <c r="D32" s="0">
-        <v>0.036063760728968788</v>
+        <v>3.0341644026639072</v>
       </c>
       <c r="E32" s="0">
-        <v>0.081744682120588247</v>
+        <v>3.5227781258390736</v>
       </c>
       <c r="F32" s="0">
-        <v>0.0072772259214787249</v>
+        <v>3.5203580395153336</v>
       </c>
       <c r="G32" s="0">
-        <v>0.040233353450010022</v>
+        <v>2.6554013277006616</v>
       </c>
       <c r="H32" s="0">
-        <v>0.05680849855138323</v>
+        <v>2.5904675339430754</v>
       </c>
       <c r="I32" s="0">
-        <v>0.075470199201604665</v>
+        <v>4.2759826021330225</v>
       </c>
       <c r="J32" s="0">
-        <v>0.03680529996319467</v>
+        <v>3.091645196908352</v>
       </c>
       <c r="K32" s="0">
-        <v>0</v>
+        <v>5.0257731958762841</v>
       </c>
       <c r="L32" s="0">
-        <v>0.015550648462040852</v>
+        <v>3.9312039312039277</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.024613566998129346</v>
+        <v>3.5172787240326837</v>
       </c>
       <c r="B33" s="0">
-        <v>0.70175438596491169</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C33" s="0">
-        <v>0.17880013695329622</v>
+        <v>3.6584283341153165</v>
       </c>
       <c r="D33" s="0">
-        <v>0.12742528790902305</v>
+        <v>2.8851008583175028</v>
       </c>
       <c r="E33" s="0">
-        <v>0.19869327843909404</v>
+        <v>3.3473552313613144</v>
       </c>
       <c r="F33" s="0">
-        <v>0.030928210166284584</v>
+        <v>3.318415020194299</v>
       </c>
       <c r="G33" s="0">
-        <v>0.060350030175015036</v>
+        <v>2.5548179440756362</v>
       </c>
       <c r="H33" s="0">
-        <v>0.15338294608873473</v>
+        <v>2.5734249843776604</v>
       </c>
       <c r="I33" s="0">
-        <v>0.16881491926674727</v>
+        <v>4.1508609560882572</v>
       </c>
       <c r="J33" s="0">
-        <v>0.055207949944792008</v>
+        <v>2.9628266470371707</v>
       </c>
       <c r="K33" s="0">
-        <v>0.38659793814432958</v>
+        <v>3.2216494845360795</v>
       </c>
       <c r="L33" s="0">
-        <v>0.062202593848163408</v>
+        <v>3.5906447298852329</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.076302057694200981</v>
+        <v>3.261297627252139</v>
       </c>
       <c r="B34" s="0">
-        <v>1.7543859649122791</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C34" s="0">
-        <v>0.37915773722720264</v>
+        <v>3.464411164229825</v>
       </c>
       <c r="D34" s="0">
-        <v>0.29572283797754406</v>
+        <v>3.2024619527324276</v>
       </c>
       <c r="E34" s="0">
-        <v>0.42423699991049818</v>
+        <v>3.3067812285569347</v>
       </c>
       <c r="F34" s="0">
-        <v>0.072772259214787263</v>
+        <v>3.2420041480187725</v>
       </c>
       <c r="G34" s="0">
-        <v>0.24140012070006014</v>
+        <v>3.3192516596258268</v>
       </c>
       <c r="H34" s="0">
-        <v>0.48855308754189586</v>
+        <v>2.4995739362608624</v>
       </c>
       <c r="I34" s="0">
-        <v>0.36344859089193826</v>
+        <v>3.9184921848622634</v>
       </c>
       <c r="J34" s="0">
-        <v>0.11041589988958402</v>
+        <v>2.1531100478468881</v>
       </c>
       <c r="K34" s="0">
-        <v>1.1597938144329887</v>
+        <v>2.3195876288659774</v>
       </c>
       <c r="L34" s="0">
-        <v>0.16017167915902081</v>
+        <v>3.4926756445743754</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.19690853598503585</v>
+        <v>3.3400610416461714</v>
       </c>
       <c r="B35" s="0">
-        <v>2.1052631578947465</v>
+        <v>1.6666666666666745</v>
       </c>
       <c r="C35" s="0">
-        <v>0.6632090186281876</v>
+        <v>3.2475684449460585</v>
       </c>
       <c r="D35" s="0">
-        <v>0.56980741951770997</v>
+        <v>3.1663981920034767</v>
       </c>
       <c r="E35" s="0">
-        <v>0.75777917002297557</v>
+        <v>3.1922193382857631</v>
       </c>
       <c r="F35" s="0">
-        <v>0.18374995451733886</v>
+        <v>3.0582541935014516</v>
       </c>
       <c r="G35" s="0">
-        <v>0.32186682760008195</v>
+        <v>3.2991349829008403</v>
       </c>
       <c r="H35" s="0">
-        <v>0.85780832812589158</v>
+        <v>2.6529568823496117</v>
       </c>
       <c r="I35" s="0">
-        <v>0.75867410776350375</v>
+        <v>3.8132311175547833</v>
       </c>
       <c r="J35" s="0">
-        <v>0.36805299963194871</v>
+        <v>2.3555391976444717</v>
       </c>
       <c r="K35" s="0">
-        <v>1.4175257731958828</v>
+        <v>0.51546391752577558</v>
       </c>
       <c r="L35" s="0">
-        <v>0.29235219108636967</v>
+        <v>3.4569091531117011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.37658757507137902</v>
+        <v>3.3203701880476491</v>
       </c>
       <c r="B36" s="0">
-        <v>4.0350877192982422</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C36" s="0">
-        <v>1.1247923509047784</v>
+        <v>2.986342712943352</v>
       </c>
       <c r="D36" s="0">
-        <v>1.1636573461880595</v>
+        <v>3.5510783064457932</v>
       </c>
       <c r="E36" s="0">
-        <v>1.2142367015722415</v>
+        <v>3.0400668277693224</v>
       </c>
       <c r="F36" s="0">
-        <v>0.4675617654550081</v>
+        <v>2.8926973037877932</v>
       </c>
       <c r="G36" s="0">
-        <v>0.56326694830014024</v>
+        <v>3.1180848923757769</v>
       </c>
       <c r="H36" s="0">
-        <v>1.3974890643640276</v>
+        <v>3.0392546724990028</v>
       </c>
       <c r="I36" s="0">
-        <v>1.2591606919425622</v>
+        <v>3.4696431054000883</v>
       </c>
       <c r="J36" s="0">
-        <v>0.5152741994847253</v>
+        <v>2.3555391976444589</v>
       </c>
       <c r="K36" s="0">
-        <v>1.417525773195875</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L36" s="0">
-        <v>0.63135632755885862</v>
+        <v>3.3542748732622116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.76794329034163566</v>
+        <v>3.0176233139706579</v>
       </c>
       <c r="B37" s="0">
-        <v>5.8771929824561351</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C37" s="0">
-        <v>1.9072014608351597</v>
+        <v>2.9964874015648158</v>
       </c>
       <c r="D37" s="0">
-        <v>2.017166350106987</v>
+        <v>3.4789507849878558</v>
       </c>
       <c r="E37" s="0">
-        <v>1.9302485157671752</v>
+        <v>2.9404218502938604</v>
       </c>
       <c r="F37" s="0">
-        <v>0.92602699850816783</v>
+        <v>2.7835389149656127</v>
       </c>
       <c r="G37" s="0">
-        <v>1.5489841078253859</v>
+        <v>3.0175015087507515</v>
       </c>
       <c r="H37" s="0">
-        <v>2.3177867408964361</v>
+        <v>2.7154462307561187</v>
       </c>
       <c r="I37" s="0">
-        <v>2.1131655776449305</v>
+        <v>3.1995392345732925</v>
       </c>
       <c r="J37" s="0">
-        <v>1.2145748987854241</v>
+        <v>2.7603974972395999</v>
       </c>
       <c r="K37" s="0">
-        <v>3.479381443298966</v>
+        <v>0</v>
       </c>
       <c r="L37" s="0">
-        <v>1.0558890305725739</v>
+        <v>2.9950548937890682</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>1.1937579994092733</v>
+        <v>3.1456138623609307</v>
       </c>
       <c r="B38" s="0">
-        <v>6.6666666666666607</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C38" s="0">
-        <v>2.6414232998135891</v>
+        <v>2.6781977960663945</v>
       </c>
       <c r="D38" s="0">
-        <v>2.9524198783449109</v>
+        <v>3.2938234799124824</v>
       </c>
       <c r="E38" s="0">
-        <v>2.5525821176049384</v>
+        <v>2.7632089262806145</v>
       </c>
       <c r="F38" s="0">
-        <v>1.5336753629516415</v>
+        <v>2.6816577520649107</v>
       </c>
       <c r="G38" s="0">
-        <v>2.2128344397505515</v>
+        <v>2.2731844699255661</v>
       </c>
       <c r="H38" s="0">
-        <v>3.2267227177185678</v>
+        <v>2.8404249275691615</v>
       </c>
       <c r="I38" s="0">
-        <v>3.0148358523167338</v>
+        <v>3.1141387460030559</v>
       </c>
       <c r="J38" s="0">
-        <v>1.9506808980493173</v>
+        <v>2.8156054471843919</v>
       </c>
       <c r="K38" s="0">
-        <v>4.8969072164948413</v>
+        <v>0</v>
       </c>
       <c r="L38" s="0">
-        <v>1.6545889963611469</v>
+        <v>2.8690946412465377</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>1.9223195825539021</v>
+        <v>2.7788717140888033</v>
       </c>
       <c r="B39" s="0">
-        <v>7.7192982456140289</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C39" s="0">
-        <v>3.3895940856465305</v>
+        <v>2.6820020542994434</v>
       </c>
       <c r="D39" s="0">
-        <v>4.1497367345466749</v>
+        <v>2.6494842882215734</v>
       </c>
       <c r="E39" s="0">
-        <v>3.1623855126942901</v>
+        <v>2.7136847757987983</v>
       </c>
       <c r="F39" s="0">
-        <v>2.044900483935522</v>
+        <v>2.4724375068223972</v>
       </c>
       <c r="G39" s="0">
-        <v>3.1985515992757962</v>
+        <v>1.991550995775496</v>
       </c>
       <c r="H39" s="0">
-        <v>3.8913821507697519</v>
+        <v>2.91427597568596</v>
       </c>
       <c r="I39" s="0">
-        <v>3.7735099600802333</v>
+        <v>2.9473098846100352</v>
       </c>
       <c r="J39" s="0">
-        <v>2.8708133971291843</v>
+        <v>2.8892160471107813</v>
       </c>
       <c r="K39" s="0">
-        <v>8.2474226804123631</v>
+        <v>0</v>
       </c>
       <c r="L39" s="0">
-        <v>2.4321214194631895</v>
+        <v>2.6187292010076795</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>2.5598109678054519</v>
+        <v>2.5991926750024592</v>
       </c>
       <c r="B40" s="0">
-        <v>6.9298245614035023</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C40" s="0">
-        <v>4.0426584156532508</v>
+        <v>2.4981295730354156</v>
       </c>
       <c r="D40" s="0">
-        <v>5.0994157670761862</v>
+        <v>2.2599956723487105</v>
       </c>
       <c r="E40" s="0">
-        <v>3.629583221456484</v>
+        <v>2.6480503594975962</v>
       </c>
       <c r="F40" s="0">
-        <v>2.8690463195429876</v>
+        <v>2.3905687152057613</v>
       </c>
       <c r="G40" s="0">
-        <v>3.8624019312009623</v>
+        <v>1.6093341380004007</v>
       </c>
       <c r="H40" s="0">
-        <v>4.3969777878770619</v>
+        <v>2.6472760324944589</v>
       </c>
       <c r="I40" s="0">
-        <v>4.3852157851879765</v>
+        <v>2.8261603543127221</v>
       </c>
       <c r="J40" s="0">
-        <v>3.993375046006622</v>
+        <v>2.6131762973868211</v>
       </c>
       <c r="K40" s="0">
-        <v>9.5360824742267951</v>
+        <v>0</v>
       </c>
       <c r="L40" s="0">
-        <v>3.3449444841849876</v>
+        <v>2.6980375081640879</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.2022250664566454</v>
+        <v>2.7837944274884445</v>
       </c>
       <c r="B41" s="0">
-        <v>6.3157894736842399</v>
+        <v>0.96491228070175894</v>
       </c>
       <c r="C41" s="0">
-        <v>4.5207268669397482</v>
+        <v>2.4321890969959155</v>
       </c>
       <c r="D41" s="0">
-        <v>5.7677974659197728</v>
+        <v>1.9835068400932943</v>
       </c>
       <c r="E41" s="0">
-        <v>3.82111638175365</v>
+        <v>2.5173782034070347</v>
       </c>
       <c r="F41" s="0">
-        <v>3.549466943201268</v>
+        <v>2.3123385365498779</v>
       </c>
       <c r="G41" s="0">
-        <v>4.546368939851158</v>
+        <v>2.0921343794005329</v>
       </c>
       <c r="H41" s="0">
-        <v>4.7775947281713567</v>
+        <v>2.317786740896449</v>
       </c>
       <c r="I41" s="0">
-        <v>4.6493614823936191</v>
+        <v>2.4646978212945241</v>
       </c>
       <c r="J41" s="0">
-        <v>4.5270518954729688</v>
+        <v>2.4107471475892641</v>
       </c>
       <c r="K41" s="0">
-        <v>11.597938144329952</v>
+        <v>0</v>
       </c>
       <c r="L41" s="0">
-        <v>4.0074021086679501</v>
+        <v>2.5736323204677754</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.7781825342128545</v>
+        <v>2.6016540317022718</v>
       </c>
       <c r="B42" s="0">
-        <v>4.9122807017543817</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C42" s="0">
-        <v>4.6767014544947267</v>
+        <v>2.2584613043533377</v>
       </c>
       <c r="D42" s="0">
-        <v>5.6692231865938929</v>
+        <v>1.670954247108887</v>
       </c>
       <c r="E42" s="0">
-        <v>3.9511918613323753</v>
+        <v>2.3902861063874199</v>
       </c>
       <c r="F42" s="0">
-        <v>4.1571153076447223</v>
+        <v>2.1213113561110486</v>
       </c>
       <c r="G42" s="0">
-        <v>5.0895192114262677</v>
+        <v>1.7903842285254461</v>
       </c>
       <c r="H42" s="0">
-        <v>4.0277225472930711</v>
+        <v>2.1814463443731165</v>
       </c>
       <c r="I42" s="0">
-        <v>4.8857023693670394</v>
+        <v>2.4567535897996047</v>
       </c>
       <c r="J42" s="0">
-        <v>5.1895472948104482</v>
+        <v>2.3923444976076533</v>
       </c>
       <c r="K42" s="0">
-        <v>8.7628865979381363</v>
+        <v>0</v>
       </c>
       <c r="L42" s="0">
-        <v>4.2095605386744595</v>
+        <v>2.3294871396137196</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.9652456433986378</v>
+        <v>2.562272324505265</v>
       </c>
       <c r="B43" s="0">
-        <v>3.2456140350877161</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C43" s="0">
-        <v>4.5714503100470418</v>
+        <v>2.1963250865468731</v>
       </c>
       <c r="D43" s="0">
-        <v>5.6451806794412471</v>
+        <v>1.7406775178515599</v>
       </c>
       <c r="E43" s="0">
-        <v>3.8342432650138698</v>
+        <v>2.4057996956949768</v>
       </c>
       <c r="F43" s="0">
-        <v>4.4336498926609131</v>
+        <v>2.0849252265036551</v>
       </c>
       <c r="G43" s="0">
-        <v>4.8481190907262075</v>
+        <v>2.0720177026755162</v>
       </c>
       <c r="H43" s="0">
-        <v>3.9709140487416881</v>
+        <v>1.9598932000227216</v>
       </c>
       <c r="I43" s="0">
-        <v>4.699012929236754</v>
+        <v>2.303827133522669</v>
       </c>
       <c r="J43" s="0">
-        <v>4.987118145012877</v>
+        <v>1.6562384983437601</v>
       </c>
       <c r="K43" s="0">
-        <v>9.020618556701022</v>
+        <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>4.1908997605200096</v>
+        <v>2.2252977949180459</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.8692527321059336</v>
+        <v>2.5007384070099414</v>
       </c>
       <c r="B44" s="0">
-        <v>2.8070175438596467</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C44" s="0">
-        <v>4.4065991199482584</v>
+        <v>2.0619079623124801</v>
       </c>
       <c r="D44" s="0">
-        <v>4.7075229004880583</v>
+        <v>1.7166350106989143</v>
       </c>
       <c r="E44" s="0">
-        <v>3.7119245800889011</v>
+        <v>2.2530505086667243</v>
       </c>
       <c r="F44" s="0">
-        <v>4.2662736964669028</v>
+        <v>2.0303460320925644</v>
       </c>
       <c r="G44" s="0">
-        <v>4.4457855562261077</v>
+        <v>1.890967612150471</v>
       </c>
       <c r="H44" s="0">
-        <v>3.3176163154007812</v>
+        <v>1.8462762029199551</v>
       </c>
       <c r="I44" s="0">
-        <v>4.470616273758214</v>
+        <v>2.1330261563821953</v>
       </c>
       <c r="J44" s="0">
-        <v>5.0239234449760719</v>
+        <v>1.7482517482517468</v>
       </c>
       <c r="K44" s="0">
-        <v>7.7319587628865918</v>
+        <v>0</v>
       </c>
       <c r="L44" s="0">
-        <v>4.2266662519827038</v>
+        <v>2.1397692283768217</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>3.6280397755242655</v>
+        <v>2.3284434380230361</v>
       </c>
       <c r="B45" s="0">
-        <v>1.3157894736842093</v>
+        <v>3.0701754385964883</v>
       </c>
       <c r="C45" s="0">
-        <v>4.0667520511292272</v>
+        <v>1.8957886861360134</v>
       </c>
       <c r="D45" s="0">
-        <v>3.9790349337628892</v>
+        <v>1.7671242757194705</v>
       </c>
       <c r="E45" s="0">
-        <v>3.5317282735165096</v>
+        <v>2.1987529460902753</v>
       </c>
       <c r="F45" s="0">
-        <v>3.8860386420696398</v>
+        <v>1.8957173525452082</v>
       </c>
       <c r="G45" s="0">
-        <v>3.4600683967008616</v>
+        <v>1.9714343190504913</v>
       </c>
       <c r="H45" s="0">
-        <v>2.7949781287280553</v>
+        <v>1.823552803499402</v>
       </c>
       <c r="I45" s="0">
-        <v>4.2739965442592958</v>
+        <v>2.0357093205695995</v>
       </c>
       <c r="J45" s="0">
-        <v>4.103790945896205</v>
+        <v>1.4538093485461894</v>
       </c>
       <c r="K45" s="0">
-        <v>7.7319587628865918</v>
+        <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>4.0727148322084989</v>
+        <v>1.9671570304481678</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>3.6378852023235178</v>
+        <v>2.1241508319385627</v>
       </c>
       <c r="B46" s="0">
-        <v>1.3157894736842093</v>
+        <v>3.1578947368421026</v>
       </c>
       <c r="C46" s="0">
-        <v>3.9589647345261763</v>
+        <v>1.8412609847956463</v>
       </c>
       <c r="D46" s="0">
-        <v>3.3443127449330388</v>
+        <v>1.7863582814415873</v>
       </c>
       <c r="E46" s="0">
-        <v>3.4816074465228648</v>
+        <v>2.1790626211999147</v>
       </c>
       <c r="F46" s="0">
-        <v>3.844194593021137</v>
+        <v>1.8193064803696815</v>
       </c>
       <c r="G46" s="0">
-        <v>2.7761013880506913</v>
+        <v>1.7702675518004409</v>
       </c>
       <c r="H46" s="0">
-        <v>2.5336590353916923</v>
+        <v>2.0223825484292433</v>
       </c>
       <c r="I46" s="0">
-        <v>4.0972373934976432</v>
+        <v>1.7953963178487005</v>
       </c>
       <c r="J46" s="0">
-        <v>3.5149061464850906</v>
+        <v>1.6746411483253574</v>
       </c>
       <c r="K46" s="0">
-        <v>3.8659793814432959</v>
+        <v>0</v>
       </c>
       <c r="L46" s="0">
-        <v>3.7679221223524992</v>
+        <v>1.9329456038316781</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>3.2563749138525306</v>
+        <v>2.0946145515408192</v>
       </c>
       <c r="B47" s="0">
-        <v>0.96491228070175894</v>
+        <v>3.4210526315789633</v>
       </c>
       <c r="C47" s="0">
-        <v>3.6964709164458256</v>
+        <v>1.6954310858621162</v>
       </c>
       <c r="D47" s="0">
-        <v>3.0509941576707762</v>
+        <v>1.8055922871637138</v>
       </c>
       <c r="E47" s="0">
-        <v>3.3461618783376745</v>
+        <v>2.0149765804469202</v>
       </c>
       <c r="F47" s="0">
-        <v>3.7332168977186067</v>
+        <v>1.7992941090856249</v>
       </c>
       <c r="G47" s="0">
-        <v>3.198551599275814</v>
+        <v>1.7300341983504404</v>
       </c>
       <c r="H47" s="0">
-        <v>2.3632335397375557</v>
+        <v>1.9939782991535626</v>
       </c>
       <c r="I47" s="0">
-        <v>3.8052868860598772</v>
+        <v>1.779507854858899</v>
       </c>
       <c r="J47" s="0">
-        <v>3.036437246963577</v>
+        <v>1.8034596981965485</v>
       </c>
       <c r="K47" s="0">
-        <v>2.5773195876288777</v>
+        <v>0</v>
       </c>
       <c r="L47" s="0">
-        <v>3.7041644636581523</v>
+        <v>1.8349765185208309</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>3.2539135571526994</v>
+        <v>2.0946145515408077</v>
       </c>
       <c r="B48" s="0">
-        <v>0.96491228070175361</v>
+        <v>3.6842105263157858</v>
       </c>
       <c r="C48" s="0">
-        <v>3.4048111185787264</v>
+        <v>1.5952522857251537</v>
       </c>
       <c r="D48" s="0">
-        <v>2.9403986247685885</v>
+        <v>1.4136994205755764</v>
       </c>
       <c r="E48" s="0">
-        <v>3.2644171962170683</v>
+        <v>1.9517288701930231</v>
       </c>
       <c r="F48" s="0">
-        <v>3.5440090237601392</v>
+        <v>1.7028708656260219</v>
       </c>
       <c r="G48" s="0">
-        <v>2.4743512371756164</v>
+        <v>1.3880506940253456</v>
       </c>
       <c r="H48" s="0">
-        <v>2.5677441345225223</v>
+        <v>2.124637845821733</v>
       </c>
       <c r="I48" s="0">
-        <v>3.4458104109153709</v>
+        <v>1.592818414728604</v>
       </c>
       <c r="J48" s="0">
         <v>2.0794994479204987</v>
       </c>
       <c r="K48" s="0">
-        <v>2.0618556701030908</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L48" s="0">
-        <v>3.5097813578826202</v>
+        <v>1.7338973035175553</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>3.2243772767549443</v>
+        <v>2.0404647041449229</v>
       </c>
       <c r="B49" s="0">
-        <v>0.61403508771929771</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C49" s="0">
-        <v>3.2158662930039661</v>
+        <v>1.5559416173169822</v>
       </c>
       <c r="D49" s="0">
-        <v>3.0197388983723195</v>
+        <v>1.3319548962565804</v>
       </c>
       <c r="E49" s="0">
-        <v>3.0860109191801639</v>
+        <v>1.8347802738745174</v>
       </c>
       <c r="F49" s="0">
-        <v>3.1783284212058338</v>
+        <v>1.5646035731179262</v>
       </c>
       <c r="G49" s="0">
-        <v>2.5548179440756362</v>
+        <v>1.1064172198752757</v>
       </c>
       <c r="H49" s="0">
-        <v>2.7892972788729171</v>
+        <v>1.7497017553826035</v>
       </c>
       <c r="I49" s="0">
-        <v>3.4835455105161732</v>
+        <v>1.4855712895473761</v>
       </c>
       <c r="J49" s="0">
-        <v>1.9506808980493173</v>
+        <v>1.8954729481045254</v>
       </c>
       <c r="K49" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L49" s="0">
-        <v>3.5642086274997635</v>
+        <v>1.6530339315149427</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>3.3277542581470878</v>
+        <v>1.8829378753568953</v>
       </c>
       <c r="B50" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C50" s="0">
-        <v>3.0281895535068895</v>
+        <v>1.4189883209272234</v>
       </c>
       <c r="D50" s="0">
-        <v>3.224100209169809</v>
+        <v>1.0290193061332427</v>
       </c>
       <c r="E50" s="0">
-        <v>2.9756257644917783</v>
+        <v>1.7822727408335555</v>
       </c>
       <c r="F50" s="0">
-        <v>3.1637739693628761</v>
+        <v>1.4863733944620299</v>
       </c>
       <c r="G50" s="0">
-        <v>2.5145845906256263</v>
+        <v>1.4886340776503708</v>
       </c>
       <c r="H50" s="0">
-        <v>2.8858717264102687</v>
+        <v>1.7269783559620504</v>
       </c>
       <c r="I50" s="0">
-        <v>3.0625012412861681</v>
+        <v>1.4061289745983185</v>
       </c>
       <c r="J50" s="0">
-        <v>2.5763709974236271</v>
+        <v>1.6930437983069548</v>
       </c>
       <c r="K50" s="0">
-        <v>0</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L50" s="0">
-        <v>3.3122881224147021</v>
+        <v>1.5270736789724118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.9610121098749604</v>
+        <v>1.7967903908634424</v>
       </c>
       <c r="B51" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C51" s="0">
-        <v>2.7961298012909093</v>
+        <v>1.4494223867916141</v>
       </c>
       <c r="D51" s="0">
-        <v>3.3803765056620074</v>
+        <v>0.9160195225158071</v>
       </c>
       <c r="E51" s="0">
-        <v>2.808556341179627</v>
+        <v>1.7106715594140622</v>
       </c>
       <c r="F51" s="0">
-        <v>2.8854200778663146</v>
+        <v>1.5082050722264659</v>
       </c>
       <c r="G51" s="0">
-        <v>3.0376181854757567</v>
+        <v>1.0259505129752555</v>
       </c>
       <c r="H51" s="0">
-        <v>3.0278929727887265</v>
+        <v>1.5111060614667942</v>
       </c>
       <c r="I51" s="0">
-        <v>2.917519016504138</v>
+        <v>1.3028539651645437</v>
       </c>
       <c r="J51" s="0">
-        <v>2.4291497975708483</v>
+        <v>1.4170040485829947</v>
       </c>
       <c r="K51" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L51" s="0">
-        <v>2.9577333374801702</v>
+        <v>1.4337697882001668</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>3.1259230087624266</v>
+        <v>1.7549473269666225</v>
       </c>
       <c r="B52" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C52" s="0">
-        <v>2.7809127683587138</v>
+        <v>1.2427243561292929</v>
       </c>
       <c r="D52" s="0">
-        <v>3.476546534272591</v>
+        <v>0.82225374462048839</v>
       </c>
       <c r="E52" s="0">
-        <v>2.8013962230376777</v>
+        <v>1.6653241445150497</v>
       </c>
       <c r="F52" s="0">
-        <v>2.7580686242404369</v>
+        <v>1.4681803296583331</v>
       </c>
       <c r="G52" s="0">
-        <v>3.2186682760008014</v>
+        <v>1.1868839267752955</v>
       </c>
       <c r="H52" s="0">
-        <v>3.0619780719195564</v>
+        <v>1.3804465147986127</v>
       </c>
       <c r="I52" s="0">
-        <v>2.8142440070703634</v>
+        <v>1.2750491549323735</v>
       </c>
       <c r="J52" s="0">
-        <v>2.649981597350016</v>
+        <v>1.4538093485461894</v>
       </c>
       <c r="K52" s="0">
-        <v>0</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L52" s="0">
-        <v>2.88153516001617</v>
+        <v>1.4431001772773913</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.9191690459781405</v>
+        <v>1.6318794919759758</v>
       </c>
       <c r="B53" s="0">
-        <v>0.43859649122806976</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C53" s="0">
-        <v>2.6655169352895651</v>
+        <v>1.1755157940120964</v>
       </c>
       <c r="D53" s="0">
-        <v>3.3803765056620074</v>
+        <v>0.75493472459307986</v>
       </c>
       <c r="E53" s="0">
-        <v>2.7029445985858742</v>
+        <v>1.5513589307556894</v>
       </c>
       <c r="F53" s="0">
-        <v>2.7562493177600675</v>
+        <v>1.2662373103372981</v>
       </c>
       <c r="G53" s="0">
-        <v>2.7962180647756965</v>
+        <v>1.3277006638503308</v>
       </c>
       <c r="H53" s="0">
-        <v>2.8063398284383316</v>
+        <v>1.2043401692893248</v>
       </c>
       <c r="I53" s="0">
-        <v>2.6772060137832394</v>
+        <v>1.181704434867231</v>
       </c>
       <c r="J53" s="0">
-        <v>2.649981597350016</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K53" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L53" s="0">
-        <v>2.6809317948558431</v>
+        <v>1.3762323888906156</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.6188835286009624</v>
+        <v>1.5014275868858902</v>
       </c>
       <c r="B54" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C54" s="0">
-        <v>2.5272955528221233</v>
+        <v>1.1425455559923397</v>
       </c>
       <c r="D54" s="0">
-        <v>2.8682711033106507</v>
+        <v>0.74772197244728611</v>
       </c>
       <c r="E54" s="0">
-        <v>2.6480503594975962</v>
+        <v>1.4373937169963291</v>
       </c>
       <c r="F54" s="0">
-        <v>2.6052468798893842</v>
+        <v>1.2189353418476865</v>
       </c>
       <c r="G54" s="0">
-        <v>2.8163347415007016</v>
+        <v>1.3277006638503308</v>
       </c>
       <c r="H54" s="0">
-        <v>2.3802760893029578</v>
+        <v>1.1872976197239098</v>
       </c>
       <c r="I54" s="0">
-        <v>2.5600285992333793</v>
+        <v>1.199578955730769</v>
       </c>
       <c r="J54" s="0">
-        <v>3.0548398969451571</v>
+        <v>1.1409642988590347</v>
       </c>
       <c r="K54" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L54" s="0">
-        <v>2.6047336173918429</v>
+        <v>1.2285012285012273</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>2.7074923697942279</v>
+        <v>1.4398936693905669</v>
       </c>
       <c r="B55" s="0">
-        <v>1.5789473684210513</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C55" s="0">
-        <v>2.3421549854804122</v>
+        <v>1.1311327812931933</v>
       </c>
       <c r="D55" s="0">
-        <v>2.4114634674103796</v>
+        <v>0.77657298103046113</v>
       </c>
       <c r="E55" s="0">
-        <v>2.465467346877888</v>
+        <v>1.3371520630090383</v>
       </c>
       <c r="F55" s="0">
-        <v>2.4633409744205488</v>
+        <v>1.2498635520139712</v>
       </c>
       <c r="G55" s="0">
-        <v>2.4140012070006014</v>
+        <v>1.2673506336753158</v>
       </c>
       <c r="H55" s="0">
-        <v>1.8974038516162002</v>
+        <v>1.334999715957506</v>
       </c>
       <c r="I55" s="0">
-        <v>2.3653949276081883</v>
+        <v>1.0148755734742101</v>
       </c>
       <c r="J55" s="0">
-        <v>2.7603974972395999</v>
+        <v>0.92013249907986661</v>
       </c>
       <c r="K55" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L55" s="0">
-        <v>2.5456411532360876</v>
+        <v>1.2238360339626151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>2.7025696563946022</v>
+        <v>1.2159102097075898</v>
       </c>
       <c r="B56" s="0">
-        <v>2.8947368421052606</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C56" s="0">
-        <v>2.3421549854804122</v>
+        <v>1.0563157027098991</v>
       </c>
       <c r="D56" s="0">
-        <v>1.937826076503256</v>
+        <v>0.66838169884355481</v>
       </c>
       <c r="E56" s="0">
-        <v>2.3807392821981543</v>
+        <v>1.2178167606432162</v>
       </c>
       <c r="F56" s="0">
-        <v>2.3123385365498654</v>
+        <v>1.1170541789469846</v>
       </c>
       <c r="G56" s="0">
-        <v>1.8507342587004612</v>
+        <v>1.0259505129752555</v>
       </c>
       <c r="H56" s="0">
-        <v>1.8462762029199551</v>
+        <v>1.2441061182752928</v>
       </c>
       <c r="I56" s="0">
-        <v>2.099263172528846</v>
+        <v>0.94536354789378485</v>
       </c>
       <c r="J56" s="0">
-        <v>2.2819285977180694</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K56" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L56" s="0">
-        <v>2.3201567505364955</v>
+        <v>1.0869903274966555</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.4933543369105307</v>
+        <v>1.289750910701992</v>
       </c>
       <c r="B57" s="0">
-        <v>3.5087719298245972</v>
+        <v>0.087719298245614932</v>
       </c>
       <c r="C57" s="0">
-        <v>2.1329207826627492</v>
+        <v>0.9979837431364943</v>
       </c>
       <c r="D57" s="0">
-        <v>1.7959752843026653</v>
+        <v>0.65876469598250376</v>
       </c>
       <c r="E57" s="0">
-        <v>2.4260866970971935</v>
+        <v>1.0913213401354567</v>
       </c>
       <c r="F57" s="0">
-        <v>2.2595786486191698</v>
+        <v>1.0533784521340572</v>
       </c>
       <c r="G57" s="0">
-        <v>1.8507342587004818</v>
+        <v>1.0259505129752671</v>
       </c>
       <c r="H57" s="0">
-        <v>1.8689996023405293</v>
+        <v>1.2384252684201682</v>
       </c>
       <c r="I57" s="0">
-        <v>1.9959881630950929</v>
+        <v>0.9056423904192662</v>
       </c>
       <c r="J57" s="0">
-        <v>2.0610967979389243</v>
+        <v>0.97534044902466954</v>
       </c>
       <c r="K57" s="0">
         <v>0.12886597938144462</v>
       </c>
       <c r="L57" s="0">
-        <v>2.1615401362237026</v>
+        <v>1.1040960408049128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>2.3481342916215397</v>
+        <v>1.1076105149158206</v>
       </c>
       <c r="B58" s="0">
-        <v>2.8947368421052606</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C58" s="0">
-        <v>2.0061121748944299</v>
+        <v>0.88766025437806639</v>
       </c>
       <c r="D58" s="0">
-        <v>1.8224220421705559</v>
+        <v>0.54095641093453173</v>
       </c>
       <c r="E58" s="0">
-        <v>2.2608073033205027</v>
+        <v>1.0191234822041222</v>
       </c>
       <c r="F58" s="0">
-        <v>2.1067569042680909</v>
+        <v>1.0133537095659126</v>
       </c>
       <c r="G58" s="0">
-        <v>2.1323677328505313</v>
+        <v>0.88513377590022047</v>
       </c>
       <c r="H58" s="0">
-        <v>1.823552803499402</v>
+        <v>1.1248082713173882</v>
       </c>
       <c r="I58" s="0">
-        <v>1.8986713272824751</v>
+        <v>0.77456257075331114</v>
       </c>
       <c r="J58" s="0">
-        <v>1.8034596981965385</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
       </c>
       <c r="L58" s="0">
-        <v>2.0386900133735559</v>
+        <v>1.0310079930333087</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>2.4022841390174241</v>
+        <v>1.1592990056118924</v>
       </c>
       <c r="B59" s="0">
-        <v>3.8596491228070144</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C59" s="0">
-        <v>1.8957886861360134</v>
+        <v>0.84074106950379712</v>
       </c>
       <c r="D59" s="0">
-        <v>1.7190392614141787</v>
+        <v>0.41833962445603795</v>
       </c>
       <c r="E59" s="0">
-        <v>2.1605656493332122</v>
+        <v>0.97795280288791342</v>
       </c>
       <c r="F59" s="0">
-        <v>2.0012371284066495</v>
+        <v>0.93876214387075552</v>
       </c>
       <c r="G59" s="0">
-        <v>2.1323677328505313</v>
+        <v>0.80466706900020035</v>
       </c>
       <c r="H59" s="0">
-        <v>2.0791910469806267</v>
+        <v>1.0964040220416964</v>
       </c>
       <c r="I59" s="0">
-        <v>1.783479970606342</v>
+        <v>0.81229767035411338</v>
       </c>
       <c r="J59" s="0">
-        <v>1.4170040485829947</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K59" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L59" s="0">
-        <v>1.9111746959848208</v>
+        <v>0.99990669610922689</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>2.1389189721374402</v>
+        <v>1.0460765974204973</v>
       </c>
       <c r="B60" s="0">
-        <v>3.6842105263157858</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C60" s="0">
-        <v>1.8057545746205235</v>
+        <v>0.82298786441623584</v>
       </c>
       <c r="D60" s="0">
-        <v>1.7983795350179099</v>
+        <v>0.41593537374077327</v>
       </c>
       <c r="E60" s="0">
-        <v>2.0722575255825038</v>
+        <v>0.94036218264267946</v>
       </c>
       <c r="F60" s="0">
-        <v>1.9921405960048013</v>
+        <v>0.94603936979223446</v>
       </c>
       <c r="G60" s="0">
-        <v>2.0720177026755162</v>
+        <v>0.64373365520016035</v>
       </c>
       <c r="H60" s="0">
-        <v>2.0223825484292433</v>
+        <v>0.97142532522865332</v>
       </c>
       <c r="I60" s="0">
-        <v>1.6980794820361049</v>
+        <v>0.69909237155170645</v>
       </c>
       <c r="J60" s="0">
-        <v>1.4538093485461894</v>
+        <v>1.0121457489878534</v>
       </c>
       <c r="K60" s="0">
         <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>1.8878487232917596</v>
+        <v>0.91126799987559404</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>2.2127596731318286</v>
+        <v>0.94269961602835406</v>
       </c>
       <c r="B61" s="0">
-        <v>1.3157894736842093</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C61" s="0">
-        <v>1.7677119922900351</v>
+        <v>0.75831547445440528</v>
       </c>
       <c r="D61" s="0">
-        <v>1.7118265092683849</v>
+        <v>0.29572283797754406</v>
       </c>
       <c r="E61" s="0">
-        <v>2.0125898743995925</v>
+        <v>0.79775649631552181</v>
       </c>
       <c r="F61" s="0">
-        <v>1.877524287741511</v>
+        <v>0.83506167448968383</v>
       </c>
       <c r="G61" s="0">
-        <v>1.9513176423254861</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H61" s="0">
-        <v>1.9769357495881366</v>
+        <v>0.98846787479406828</v>
       </c>
       <c r="I61" s="0">
-        <v>1.6027487040972361</v>
+        <v>0.69909237155170645</v>
       </c>
       <c r="J61" s="0">
-        <v>1.821862348178136</v>
+        <v>0.95693779904306131</v>
       </c>
       <c r="K61" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.7774391192112695</v>
+        <v>0.90971293502938988</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>2.0503101309441747</v>
+        <v>0.80486364083882966</v>
       </c>
       <c r="B62" s="0">
-        <v>1.6666666666666652</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C62" s="0">
-        <v>1.6231501794341785</v>
+        <v>0.67208562117196458</v>
       </c>
       <c r="D62" s="0">
-        <v>1.6757627485394162</v>
+        <v>0.26687182939436899</v>
       </c>
       <c r="E62" s="0">
-        <v>1.9201050150660801</v>
+        <v>0.72018854977773739</v>
       </c>
       <c r="F62" s="0">
-        <v>1.8502346905359659</v>
+        <v>0.80049485136265985</v>
       </c>
       <c r="G62" s="0">
-        <v>1.7903842285254461</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H62" s="0">
-        <v>1.9201272510367535</v>
+        <v>0.77827643015395032</v>
       </c>
       <c r="I62" s="0">
-        <v>1.5252924470219049</v>
+        <v>0.60177553573911091</v>
       </c>
       <c r="J62" s="0">
-        <v>1.8402649981597332</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K62" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.6437035424377182</v>
+        <v>0.81329891456473657</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>2.072462341242491</v>
+        <v>0.792556857339765</v>
       </c>
       <c r="B63" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C63" s="0">
-        <v>1.4621032475684437</v>
+        <v>0.63657921099684189</v>
       </c>
       <c r="D63" s="0">
-        <v>1.6396989878104475</v>
+        <v>0.2163825643738127</v>
       </c>
       <c r="E63" s="0">
-        <v>1.8341835973626883</v>
+        <v>0.68617798860347801</v>
       </c>
       <c r="F63" s="0">
-        <v>1.7174253174689793</v>
+        <v>0.70589091438343643</v>
       </c>
       <c r="G63" s="0">
-        <v>1.8708509354254659</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H63" s="0">
-        <v>1.7269783559620504</v>
+        <v>0.80668067942964195</v>
       </c>
       <c r="I63" s="0">
-        <v>1.3525054120077047</v>
+        <v>0.60574765148656373</v>
       </c>
       <c r="J63" s="0">
-        <v>1.7482517482517468</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K63" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.6219326345908609</v>
+        <v>0.78841787702547128</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.8829378753568953</v>
+        <v>0.75071379344294509</v>
       </c>
       <c r="B64" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C64" s="0">
-        <v>1.4760521944229561</v>
+        <v>0.50596634499549786</v>
       </c>
       <c r="D64" s="0">
-        <v>1.30550813838867</v>
+        <v>0.2548505758180461</v>
       </c>
       <c r="E64" s="0">
-        <v>1.7232017661624734</v>
+        <v>0.60443330648288984</v>
       </c>
       <c r="F64" s="0">
-        <v>1.6864971073026946</v>
+        <v>0.65858894589382466</v>
       </c>
       <c r="G64" s="0">
-        <v>1.3277006638503308</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H64" s="0">
-        <v>1.4940635119013792</v>
+        <v>0.71578708174742878</v>
       </c>
       <c r="I64" s="0">
-        <v>1.312784254533176</v>
+        <v>0.51240293142142113</v>
       </c>
       <c r="J64" s="0">
-        <v>1.7850570482149415</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K64" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.5348490032034323</v>
+        <v>0.72155008863869563</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.8263266712611974</v>
+        <v>0.63749138525155003</v>
       </c>
       <c r="B65" s="0">
         <v>0.70175438596491169</v>
       </c>
       <c r="C65" s="0">
-        <v>1.3898223411405155</v>
+        <v>0.53132806654915687</v>
       </c>
       <c r="D65" s="0">
-        <v>1.2405933690765261</v>
+        <v>0.30293559012333776</v>
       </c>
       <c r="E65" s="0">
-        <v>1.683821116381752</v>
+        <v>0.54595900832363686</v>
       </c>
       <c r="F65" s="0">
-        <v>1.5773387184805139</v>
+        <v>0.69861368846195771</v>
       </c>
       <c r="G65" s="0">
-        <v>1.4484007242003607</v>
+        <v>0.74431703882518541</v>
       </c>
       <c r="H65" s="0">
-        <v>1.3577231153780593</v>
+        <v>0.55672328580355568</v>
       </c>
       <c r="I65" s="0">
-        <v>1.1459553931401552</v>
+        <v>0.48857023693670393</v>
       </c>
       <c r="J65" s="0">
-        <v>1.821862348178136</v>
+        <v>0.53367684946632266</v>
       </c>
       <c r="K65" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>1.4648710851242484</v>
+        <v>0.66245762448294032</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.7574086836664353</v>
+        <v>0.6547208821502406</v>
       </c>
       <c r="B66" s="0">
-        <v>0.52631578947368374</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C66" s="0">
-        <v>1.2845711966928304</v>
+        <v>0.47299610697574113</v>
       </c>
       <c r="D66" s="0">
-        <v>0.91121102108527796</v>
+        <v>0.30533984083860238</v>
       </c>
       <c r="E66" s="0">
-        <v>1.5782093737879994</v>
+        <v>0.47256779736865612</v>
       </c>
       <c r="F66" s="0">
-        <v>1.5154822981479448</v>
+        <v>0.62038350980606138</v>
       </c>
       <c r="G66" s="0">
-        <v>1.0460671897002607</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H66" s="0">
-        <v>1.4145316139294426</v>
+        <v>0.72714878145770534</v>
       </c>
       <c r="I66" s="0">
-        <v>1.1876626084884103</v>
+        <v>0.48062600544179812</v>
       </c>
       <c r="J66" s="0">
-        <v>1.6378358483621627</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K66" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>1.3902279725064521</v>
+        <v>0.65934749479053212</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.5309638672836454</v>
+        <v>0.54395983065865861</v>
       </c>
       <c r="B67" s="0">
-        <v>0.70175438596491169</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C67" s="0">
-        <v>1.1805881383228283</v>
+        <v>0.4286130942568378</v>
       </c>
       <c r="D67" s="0">
-        <v>0.81984949390522377</v>
+        <v>0.24763782367225232</v>
       </c>
       <c r="E67" s="0">
-        <v>1.489304573525462</v>
+        <v>0.43139711805244751</v>
       </c>
       <c r="F67" s="0">
-        <v>1.439071425972418</v>
+        <v>0.58763599315940718</v>
       </c>
       <c r="G67" s="0">
-        <v>1.4081673707503508</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H67" s="0">
-        <v>1.2838720672612611</v>
+        <v>0.61921263421007733</v>
       </c>
       <c r="I67" s="0">
-        <v>1.0089173998530307</v>
+        <v>0.45480725308335446</v>
       </c>
       <c r="J67" s="0">
-        <v>1.3065881486934106</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K67" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>1.2844835629645746</v>
+        <v>0.60958541971200153</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.4497390961898187</v>
+        <v>0.57841882445603965</v>
       </c>
       <c r="B68" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C68" s="0">
-        <v>1.1729796218567305</v>
+        <v>0.35886835998427541</v>
       </c>
       <c r="D68" s="0">
-        <v>0.72848796672516947</v>
+        <v>0.23321231938066481</v>
       </c>
       <c r="E68" s="0">
-        <v>1.4296369223425507</v>
+        <v>0.36456934872758701</v>
       </c>
       <c r="F68" s="0">
-        <v>1.3517447149146733</v>
+        <v>0.48939344321944434</v>
       </c>
       <c r="G68" s="0">
-        <v>1.3075839871253259</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H68" s="0">
-        <v>1.2952337669715377</v>
+        <v>0.64761688348576885</v>
       </c>
       <c r="I68" s="0">
-        <v>0.9374193163988791</v>
+        <v>0.35153224364957964</v>
       </c>
       <c r="J68" s="0">
-        <v>1.0857563489142428</v>
+        <v>0.66249539933750401</v>
       </c>
       <c r="K68" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>1.3015892762728194</v>
+        <v>0.49762075078530726</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.4005119621935753</v>
+        <v>0.53165304715959982</v>
       </c>
       <c r="B69" s="0">
-        <v>0.087719298245614932</v>
+        <v>1.1403508771929942</v>
       </c>
       <c r="C69" s="0">
-        <v>1.1019668015064974</v>
+        <v>0.30560874472159483</v>
       </c>
       <c r="D69" s="0">
-        <v>0.74291347101676519</v>
+        <v>0.17070180078378747</v>
       </c>
       <c r="E69" s="0">
-        <v>1.3079149139294266</v>
+        <v>0.2792446075360272</v>
       </c>
       <c r="F69" s="0">
-        <v>1.2498635520139849</v>
+        <v>0.48393552377834065</v>
       </c>
       <c r="G69" s="0">
-        <v>1.2271172802253194</v>
+        <v>0.38221685777509945</v>
       </c>
       <c r="H69" s="0">
-        <v>1.130489121172539</v>
+        <v>0.47719138783162446</v>
       </c>
       <c r="I69" s="0">
-        <v>0.9076284482929925</v>
+        <v>0.32571349129113952</v>
       </c>
       <c r="J69" s="0">
-        <v>1.0857563489142548</v>
+        <v>0.4968715495031335</v>
       </c>
       <c r="K69" s="0">
-        <v>0.64432989690722309</v>
+        <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>1.2051752558081794</v>
+        <v>0.4867352968618841</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.3512848281973011</v>
+        <v>0.51442355026090336</v>
       </c>
       <c r="B70" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0081284317579469</v>
+        <v>0.23332783829366316</v>
       </c>
       <c r="D70" s="0">
-        <v>0.76214747673887362</v>
+        <v>0.14906354434640432</v>
       </c>
       <c r="E70" s="0">
-        <v>1.2458605566991845</v>
+        <v>0.29356484381992276</v>
       </c>
       <c r="F70" s="0">
-        <v>1.3317323436306068</v>
+        <v>0.44027216824946291</v>
       </c>
       <c r="G70" s="0">
-        <v>1.1667672500502908</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H70" s="0">
-        <v>1.3122763165369529</v>
+        <v>0.51127648696244921</v>
       </c>
       <c r="I70" s="0">
-        <v>0.86194911719727441</v>
+        <v>0.2919505074377865</v>
       </c>
       <c r="J70" s="0">
-        <v>1.2881854987118135</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K70" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>1.1802942182689009</v>
+        <v>0.49451062109289917</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.1494535788126405</v>
+        <v>0.4307374224672636</v>
       </c>
       <c r="B71" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C71" s="0">
-        <v>0.95360073041757987</v>
+        <v>0.21177037497305301</v>
       </c>
       <c r="D71" s="0">
-        <v>0.71165821171831734</v>
+        <v>0.13944654148534597</v>
       </c>
       <c r="E71" s="0">
-        <v>1.0698409857095965</v>
+        <v>0.24105731077896098</v>
       </c>
       <c r="F71" s="0">
-        <v>1.1370665502310511</v>
+        <v>0.42025979696539645</v>
       </c>
       <c r="G71" s="0">
-        <v>1.0460671897002607</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H71" s="0">
-        <v>1.2611486678407078</v>
+        <v>0.40334033971482097</v>
       </c>
       <c r="I71" s="0">
-        <v>0.80435343885920763</v>
+        <v>0.25024329208953128</v>
       </c>
       <c r="J71" s="0">
-        <v>0.99374309900625601</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K71" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>1.0994308462662883</v>
+        <v>0.42453270301371532</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.0731515211184397</v>
+        <v>0.34705129467362378</v>
       </c>
       <c r="B72" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C72" s="0">
-        <v>0.92823900886392086</v>
+        <v>0.17626396479793033</v>
       </c>
       <c r="D72" s="0">
-        <v>0.60106267881614639</v>
+        <v>0.088957276464789667</v>
       </c>
       <c r="E72" s="0">
-        <v>1.0167367761568056</v>
+        <v>0.21301351472299274</v>
       </c>
       <c r="F72" s="0">
-        <v>1.1261507113488329</v>
+        <v>0.41662118400465709</v>
       </c>
       <c r="G72" s="0">
-        <v>0.92536712935023058</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H72" s="0">
-        <v>1.1361699710276647</v>
+        <v>0.46014883826620417</v>
       </c>
       <c r="I72" s="0">
-        <v>0.74477170264741444</v>
+        <v>0.28400627594288075</v>
       </c>
       <c r="J72" s="0">
-        <v>0.88332719911667212</v>
+        <v>0.58888479941111471</v>
       </c>
       <c r="K72" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L72" s="0">
-        <v>0.98591111249339003</v>
+        <v>0.42764283270612352</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.0534606675199361</v>
+        <v>0.3273604410751203</v>
       </c>
       <c r="B73" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C73" s="0">
-        <v>0.80016231501794266</v>
+        <v>0.12173626345756339</v>
       </c>
       <c r="D73" s="0">
-        <v>0.57221167023297137</v>
+        <v>0.081744524318995912</v>
       </c>
       <c r="E73" s="0">
-        <v>0.93021868194158452</v>
+        <v>0.18198633610787895</v>
       </c>
       <c r="F73" s="0">
-        <v>1.0370046938107185</v>
+        <v>0.32383655350580332</v>
       </c>
       <c r="G73" s="0">
-        <v>1.1667672500502908</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H73" s="0">
-        <v>1.0793614724762814</v>
+        <v>0.30676589217746947</v>
       </c>
       <c r="I73" s="0">
-        <v>0.69114814005680059</v>
+        <v>0.26414569720561632</v>
       </c>
       <c r="J73" s="0">
-        <v>0.95693779904306131</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.9874661773395943</v>
+        <v>0.35144465524212326</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.91562469233041177</v>
+        <v>0.33228315447474616</v>
       </c>
       <c r="B74" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C74" s="0">
-        <v>0.79128571247416202</v>
+        <v>0.10271497229231912</v>
       </c>
       <c r="D74" s="0">
-        <v>0.45680763590027129</v>
+        <v>0.084148775034260492</v>
       </c>
       <c r="E74" s="0">
-        <v>0.80789999701661674</v>
+        <v>0.16169933470568917</v>
       </c>
       <c r="F74" s="0">
-        <v>0.94422006331186481</v>
+        <v>0.23469053596768888</v>
       </c>
       <c r="G74" s="0">
-        <v>1.0259505129752555</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H74" s="0">
-        <v>0.77827643015395032</v>
+        <v>0.29540419246719279</v>
       </c>
       <c r="I74" s="0">
-        <v>0.64745486683481901</v>
+        <v>0.22045242398363471</v>
       </c>
       <c r="J74" s="0">
-        <v>0.95693779904306131</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.96880539918514519</v>
+        <v>0.31878829347183751</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.95500639952741873</v>
+        <v>0.2535197400807323</v>
       </c>
       <c r="B75" s="0">
-        <v>1.0526315789473675</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.74436652759989286</v>
+        <v>0.084961767204757788</v>
       </c>
       <c r="D75" s="0">
-        <v>0.43516937946288997</v>
+        <v>0.069723270742672983</v>
       </c>
       <c r="E75" s="0">
-        <v>0.760762552582117</v>
+        <v>0.13544556818520828</v>
       </c>
       <c r="F75" s="0">
-        <v>0.89691809482225293</v>
+        <v>0.27289597205545219</v>
       </c>
       <c r="G75" s="0">
-        <v>0.96560048280024058</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H75" s="0">
-        <v>0.8634891779810252</v>
+        <v>0.24995739362608624</v>
       </c>
       <c r="I75" s="0">
-        <v>0.61965005660264882</v>
+        <v>0.17278703501420015</v>
       </c>
       <c r="J75" s="0">
-        <v>1.0121457489878534</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.80707865517992028</v>
+        <v>0.27058128323951086</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.78025007384070022</v>
+        <v>0.2338288864822288</v>
       </c>
       <c r="B76" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C76" s="0">
-        <v>0.69871542880330662</v>
+        <v>0.059600045651098742</v>
       </c>
       <c r="D76" s="0">
-        <v>0.36063760728968786</v>
+        <v>0.084148775034260492</v>
       </c>
       <c r="E76" s="0">
-        <v>0.70228825442286402</v>
+        <v>0.11396521375936026</v>
       </c>
       <c r="F76" s="0">
-        <v>0.90965324018484073</v>
+        <v>0.18193064803696812</v>
       </c>
       <c r="G76" s="0">
-        <v>0.60350030175015035</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H76" s="0">
-        <v>0.77827643015395032</v>
+        <v>0.24427654377094793</v>
       </c>
       <c r="I76" s="0">
-        <v>0.5382216837798649</v>
+        <v>0.15888462989811508</v>
       </c>
       <c r="J76" s="0">
-        <v>0.92013249907986661</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L76" s="0">
-        <v>0.77131216371722633</v>
+        <v>0.26747115354710271</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.85162941813527537</v>
+        <v>0.20183124938466063</v>
       </c>
       <c r="B77" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C77" s="0">
-        <v>0.65306433000672026</v>
+        <v>0.044383012718903318</v>
       </c>
       <c r="D77" s="0">
-        <v>0.28129733368595655</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E77" s="0">
-        <v>0.60980339508935177</v>
+        <v>0.088904800262537581</v>
       </c>
       <c r="F77" s="0">
-        <v>0.82414583560746568</v>
+        <v>0.17101480915475006</v>
       </c>
       <c r="G77" s="0">
-        <v>0.70408368537517541</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H77" s="0">
-        <v>0.68738283247173715</v>
+        <v>0.21019144464011796</v>
       </c>
       <c r="I77" s="0">
-        <v>0.54020774165359131</v>
+        <v>0.12313558817103919</v>
       </c>
       <c r="J77" s="0">
-        <v>0.77291129922708801</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L77" s="0">
-        <v>0.73554567225453238</v>
+        <v>0.21926414331477603</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.70887072954612518</v>
+        <v>0.16983361228709251</v>
       </c>
       <c r="B78" s="0">
-        <v>1.2280701754385954</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>0.55034935771440119</v>
+        <v>0.034238324097439703</v>
       </c>
       <c r="D78" s="0">
-        <v>0.27889308297069193</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E78" s="0">
-        <v>0.56564933321399757</v>
+        <v>0.072197857931322468</v>
       </c>
       <c r="F78" s="0">
-        <v>0.7823017865589631</v>
+        <v>0.098242549939962814</v>
       </c>
       <c r="G78" s="0">
-        <v>0.82478374572520541</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H78" s="0">
-        <v>0.71578708174742878</v>
+        <v>0.17610634550928805</v>
       </c>
       <c r="I78" s="0">
-        <v>0.50048658417906255</v>
+        <v>0.08341443069651043</v>
       </c>
       <c r="J78" s="0">
-        <v>0.73610599926389342</v>
+        <v>0.11041589988958402</v>
       </c>
       <c r="K78" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L78" s="0">
-        <v>0.71377476440767518</v>
+        <v>0.16328180885142896</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.62518460175248536</v>
+        <v>0.1624495421876537</v>
       </c>
       <c r="B79" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C79" s="0">
-        <v>0.47553227913110702</v>
+        <v>0.016485119009878375</v>
       </c>
       <c r="D79" s="0">
-        <v>0.2548505758180461</v>
+        <v>0.028851008583175027</v>
       </c>
       <c r="E79" s="0">
-        <v>0.48569468062889659</v>
+        <v>0.048330797458158013</v>
       </c>
       <c r="F79" s="0">
-        <v>0.75137357639267843</v>
+        <v>0.098242549939962814</v>
       </c>
       <c r="G79" s="0">
-        <v>0.48280024140012029</v>
+        <v>0.12070006035003007</v>
       </c>
       <c r="H79" s="0">
-        <v>0.70442538203715221</v>
+        <v>0.13634039652331978</v>
       </c>
       <c r="I79" s="0">
-        <v>0.38728128537665557</v>
+        <v>0.089372604317689744</v>
       </c>
       <c r="J79" s="0">
-        <v>0.62569009937430942</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K79" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L79" s="0">
-        <v>0.68889372686840977</v>
+        <v>0.12907038223493908</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.60057103475435603</v>
+        <v>0.12060647829083379</v>
       </c>
       <c r="B80" s="0">
-        <v>1.0526315789473675</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C80" s="0">
-        <v>0.48187270951952171</v>
+        <v>0.021557463320610183</v>
       </c>
       <c r="D80" s="0">
-        <v>0.27648883225542736</v>
+        <v>0.043276512874762536</v>
       </c>
       <c r="E80" s="0">
-        <v>0.45586085503744106</v>
+        <v>0.042364032339866901</v>
       </c>
       <c r="F80" s="0">
-        <v>0.65495033293308536</v>
+        <v>0.070952952734417582</v>
       </c>
       <c r="G80" s="0">
-        <v>0.90525045262522552</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H80" s="0">
-        <v>0.68738283247173715</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I80" s="0">
-        <v>0.40714186411391989</v>
+        <v>0.061567794085519593</v>
       </c>
       <c r="J80" s="0">
-        <v>0.71770334928229607</v>
+        <v>0.12881854987118133</v>
       </c>
       <c r="K80" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L80" s="0">
-        <v>0.65312723540571582</v>
+        <v>0.091748825926041028</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.55872797085753612</v>
+        <v>0.095992911292704458</v>
       </c>
       <c r="B81" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C81" s="0">
-        <v>0.4197364917130571</v>
+        <v>0.0088766025437806654</v>
       </c>
       <c r="D81" s="0">
-        <v>0.26446757867910442</v>
+        <v>0.019234005722116688</v>
       </c>
       <c r="E81" s="0">
-        <v>0.37769623198782748</v>
+        <v>0.032220531638772011</v>
       </c>
       <c r="F81" s="0">
-        <v>0.60764836444347359</v>
+        <v>0.047301968489611719</v>
       </c>
       <c r="G81" s="0">
-        <v>0.52303359485013035</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H81" s="0">
-        <v>0.62489348406521561</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I81" s="0">
-        <v>0.3614625330182118</v>
+        <v>0.047665388969434529</v>
       </c>
       <c r="J81" s="0">
-        <v>0.79131394920868536</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K81" s="0">
-        <v>0</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L81" s="0">
-        <v>0.63602152209747087</v>
+        <v>0.080863372002612441</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.61041646155361462</v>
+        <v>0.088608841193266633</v>
       </c>
       <c r="B82" s="0">
-        <v>0.61403508771930448</v>
+        <v>0.17543859649122986</v>
       </c>
       <c r="C82" s="0">
-        <v>0.35886835998427941</v>
+        <v>0.010144688621463728</v>
       </c>
       <c r="D82" s="0">
-        <v>0.22119106580434433</v>
+        <v>0.014425504291587673</v>
       </c>
       <c r="E82" s="0">
-        <v>0.33950893523076814</v>
+        <v>0.019690324890360891</v>
       </c>
       <c r="F82" s="0">
-        <v>0.56034639595386815</v>
+        <v>0.036386129607394034</v>
       </c>
       <c r="G82" s="0">
-        <v>0.50291691812513084</v>
+        <v>0.040233353450010473</v>
       </c>
       <c r="H82" s="0">
-        <v>0.56240413565870029</v>
+        <v>0.07953189797193741</v>
       </c>
       <c r="I82" s="0">
-        <v>0.29592262318524265</v>
+        <v>0.03574904172707629</v>
       </c>
       <c r="J82" s="0">
-        <v>0.4968715495031335</v>
+        <v>0.018402649981597536</v>
       </c>
       <c r="K82" s="0">
-        <v>0.12886597938144462</v>
+        <v>1.1597938144330016</v>
       </c>
       <c r="L82" s="0">
-        <v>0.51939165863217029</v>
+        <v>0.062202593848164102</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.5021167667618387</v>
+        <v>0.066456630894949242</v>
       </c>
       <c r="B83" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C83" s="0">
-        <v>0.29800022825549372</v>
+        <v>0.0050723443107318078</v>
       </c>
       <c r="D83" s="0">
-        <v>0.24042507152645856</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E83" s="0">
-        <v>0.31743190429308721</v>
+        <v>0.010740177212924003</v>
       </c>
       <c r="F83" s="0">
-        <v>0.54397263763053472</v>
+        <v>0.016373758323327131</v>
       </c>
       <c r="G83" s="0">
-        <v>0.54315027157513529</v>
+        <v>0</v>
       </c>
       <c r="H83" s="0">
-        <v>0.53968073623814072</v>
+        <v>0.051127648696244914</v>
       </c>
       <c r="I83" s="0">
-        <v>0.26414569720561631</v>
+        <v>0.041707215348255215</v>
       </c>
       <c r="J83" s="0">
-        <v>0.36805299963194671</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K83" s="0">
-        <v>0</v>
+        <v>1.2886597938144317</v>
       </c>
       <c r="L83" s="0">
-        <v>0.58314931732653197</v>
+        <v>0.041986750847510308</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.43812149256670241</v>
+        <v>0.03199763709756815</v>
       </c>
       <c r="B84" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C84" s="0">
-        <v>0.25234912945890747</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D84" s="0">
-        <v>0.18753155579063768</v>
+        <v>0</v>
       </c>
       <c r="E84" s="0">
-        <v>0.28521137265431518</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F84" s="0">
-        <v>0.4930320561801837</v>
+        <v>0.010915838882218089</v>
       </c>
       <c r="G84" s="0">
-        <v>0.40233353450010018</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H84" s="0">
-        <v>0.4317445889905126</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I84" s="0">
-        <v>0.30585291255387154</v>
+        <v>0.0099302893686321926</v>
       </c>
       <c r="J84" s="0">
-        <v>0.4600662495399333</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K84" s="0">
-        <v>0</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L84" s="0">
-        <v>0.45563399993779702</v>
+        <v>0.032656361770285788</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.45535098946539293</v>
+        <v>0.039381707197006954</v>
       </c>
       <c r="B85" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C85" s="0">
-        <v>0.20162568635158939</v>
+        <v>0</v>
       </c>
       <c r="D85" s="0">
-        <v>0.16589329935325642</v>
+        <v>0</v>
       </c>
       <c r="E85" s="0">
-        <v>0.2523941645037141</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F85" s="0">
-        <v>0.48575483025870497</v>
+        <v>0.010915838882218089</v>
       </c>
       <c r="G85" s="0">
-        <v>0.40233353450010018</v>
+        <v>0</v>
       </c>
       <c r="H85" s="0">
-        <v>0.34653184116343771</v>
+        <v>0.039765948985968268</v>
       </c>
       <c r="I85" s="0">
-        <v>0.23634088697344621</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J85" s="0">
-        <v>0.47846889952153066</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K85" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L85" s="0">
-        <v>0.37010543339657231</v>
+        <v>0.010885453923428597</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.41596928226838598</v>
+        <v>0.014768140198877608</v>
       </c>
       <c r="B86" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C86" s="0">
-        <v>0.13948946854512473</v>
+        <v>0</v>
       </c>
       <c r="D86" s="0">
-        <v>0.11540403433270011</v>
+        <v>0</v>
       </c>
       <c r="E86" s="0">
-        <v>0.21719025030579653</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F86" s="0">
-        <v>0.43117563584761448</v>
+        <v>0</v>
       </c>
       <c r="G86" s="0">
-        <v>0.20116676725005009</v>
+        <v>0</v>
       </c>
       <c r="H86" s="0">
-        <v>0.32948929159802276</v>
+        <v>0.017042549565414972</v>
       </c>
       <c r="I86" s="0">
-        <v>0.18867549800401168</v>
+        <v>0.0099302893686321926</v>
       </c>
       <c r="J86" s="0">
-        <v>0.44166359955833606</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K86" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L86" s="0">
-        <v>0.38254595216620496</v>
+        <v>0.013995583615836769</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.35443536477306259</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B87" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C87" s="0">
-        <v>0.13441712423439289</v>
+        <v>0</v>
       </c>
       <c r="D87" s="0">
-        <v>0.10338278075637719</v>
+        <v>0</v>
       </c>
       <c r="E87" s="0">
-        <v>0.16229601121751827</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F87" s="0">
-        <v>0.3765964414365241</v>
+        <v>0.0054579194411090446</v>
       </c>
       <c r="G87" s="0">
-        <v>0.30175015087507517</v>
+        <v>0</v>
       </c>
       <c r="H87" s="0">
-        <v>0.34653184116343771</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I87" s="0">
-        <v>0.2005918452463703</v>
+        <v>0.0079442314949057548</v>
       </c>
       <c r="J87" s="0">
-        <v>0.42326094957673871</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K87" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L87" s="0">
-        <v>0.37632569278138867</v>
+        <v>0.010885453923428597</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.27813330707886164</v>
+        <v>0.0098454267992517386</v>
       </c>
       <c r="B88" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C88" s="0">
-        <v>0.098910714059270252</v>
+        <v>0</v>
       </c>
       <c r="D88" s="0">
-        <v>0.079340273603731332</v>
+        <v>0</v>
       </c>
       <c r="E88" s="0">
-        <v>0.15334586354008159</v>
+        <v>0</v>
       </c>
       <c r="F88" s="0">
-        <v>0.32929447294691233</v>
+        <v>0</v>
       </c>
       <c r="G88" s="0">
-        <v>0.30175015087507517</v>
+        <v>0</v>
       </c>
       <c r="H88" s="0">
-        <v>0.2158722944952563</v>
+        <v>0</v>
       </c>
       <c r="I88" s="0">
-        <v>0.15292645627693577</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J88" s="0">
-        <v>0.40485829959514136</v>
+        <v>0</v>
       </c>
       <c r="K88" s="0">
-        <v>0</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L88" s="0">
-        <v>0.35766491462693961</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.24121295658166758</v>
+        <v>0.0049227133996258693</v>
       </c>
       <c r="B89" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C89" s="0">
-        <v>0.07988942289402598</v>
+        <v>0</v>
       </c>
       <c r="D89" s="0">
-        <v>0.091361527180054247</v>
+        <v>0</v>
       </c>
       <c r="E89" s="0">
-        <v>0.12947880306691717</v>
+        <v>0</v>
       </c>
       <c r="F89" s="0">
-        <v>0.28381181093767033</v>
+        <v>0</v>
       </c>
       <c r="G89" s="0">
-        <v>0.32186682760008017</v>
+        <v>0</v>
       </c>
       <c r="H89" s="0">
-        <v>0.23859569391580959</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I89" s="0">
-        <v>0.12710770391849208</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J89" s="0">
-        <v>0.22083179977916803</v>
+        <v>0</v>
       </c>
       <c r="K89" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L89" s="0">
-        <v>0.28302180200914351</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.20921531948409947</v>
+        <v>0</v>
       </c>
       <c r="B90" s="0">
         <v>0</v>
       </c>
       <c r="C90" s="0">
-        <v>0.065940476039513501</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.074531772173202157</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0">
-        <v>0.11098183120021471</v>
+        <v>0</v>
       </c>
       <c r="F90" s="0">
-        <v>0.28745042389840969</v>
+        <v>0</v>
       </c>
       <c r="G90" s="0">
-        <v>0.14081673707503506</v>
+        <v>0</v>
       </c>
       <c r="H90" s="0">
-        <v>0.24427654377094793</v>
+        <v>0</v>
       </c>
       <c r="I90" s="0">
-        <v>0.13505193541339783</v>
+        <v>0</v>
       </c>
       <c r="J90" s="0">
-        <v>0.165623849834376</v>
+        <v>0</v>
       </c>
       <c r="K90" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L90" s="0">
-        <v>0.22392933785338831</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.17229496898690544</v>
+        <v>0</v>
       </c>
       <c r="B91" s="0">
         <v>0</v>
       </c>
       <c r="C91" s="0">
-        <v>0.041846840563537414</v>
+        <v>0</v>
       </c>
       <c r="D91" s="0">
-        <v>0.072127521457937577</v>
+        <v>0</v>
       </c>
       <c r="E91" s="0">
-        <v>0.081148005608759136</v>
+        <v>0</v>
       </c>
       <c r="F91" s="0">
-        <v>0.22741331004621018</v>
+        <v>0</v>
       </c>
       <c r="G91" s="0">
-        <v>0.16093341380004009</v>
+        <v>0</v>
       </c>
       <c r="H91" s="0">
-        <v>0.2158722944952563</v>
+        <v>0</v>
       </c>
       <c r="I91" s="0">
-        <v>0.069512025580425352</v>
+        <v>0</v>
       </c>
       <c r="J91" s="0">
-        <v>0.25763709974236265</v>
+        <v>0</v>
       </c>
       <c r="K91" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L91" s="0">
-        <v>0.19749323546791883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.19444717928522184</v>
+        <v>0</v>
       </c>
       <c r="B92" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0.025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D92" s="0">
-        <v>0.06010626788161464</v>
+        <v>0</v>
       </c>
       <c r="E92" s="0">
-        <v>0.059070974671082015</v>
+        <v>0</v>
       </c>
       <c r="F92" s="0">
-        <v>0.17101480915475006</v>
+        <v>0</v>
       </c>
       <c r="G92" s="0">
-        <v>0.16093341380004009</v>
+        <v>0</v>
       </c>
       <c r="H92" s="0">
-        <v>0.10793614724762815</v>
+        <v>0</v>
       </c>
       <c r="I92" s="0">
-        <v>0.089372604317689744</v>
+        <v>0</v>
       </c>
       <c r="J92" s="0">
-        <v>0.11041589988958402</v>
+        <v>0</v>
       </c>
       <c r="K92" s="0">
         <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>0.15395141977420446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.13291326178989848</v>
+        <v>0</v>
       </c>
       <c r="B93" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C93" s="0">
-        <v>0.020289377242927231</v>
+        <v>0</v>
       </c>
       <c r="D93" s="0">
-        <v>0.074531772173202157</v>
+        <v>0</v>
       </c>
       <c r="E93" s="0">
-        <v>0.039380649780721345</v>
+        <v>0</v>
       </c>
       <c r="F93" s="0">
-        <v>0.16009897027253195</v>
+        <v>0</v>
       </c>
       <c r="G93" s="0">
-        <v>0.10058338362502504</v>
+        <v>0</v>
       </c>
       <c r="H93" s="0">
-        <v>0.11361699710276646</v>
+        <v>0</v>
       </c>
       <c r="I93" s="0">
-        <v>0.061567794085519593</v>
+        <v>0</v>
       </c>
       <c r="J93" s="0">
-        <v>0.092013249907986677</v>
+        <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L93" s="0">
-        <v>0.13840077131216358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.14522004528896476</v>
+        <v>0</v>
       </c>
       <c r="B94" s="0">
-        <v>0.087719298245614932</v>
+        <v>0</v>
       </c>
       <c r="C94" s="0">
-        <v>0.021557463320610423</v>
+        <v>0</v>
       </c>
       <c r="D94" s="0">
-        <v>0.052893515735821468</v>
+        <v>0</v>
       </c>
       <c r="E94" s="0">
-        <v>0.041170679316209137</v>
+        <v>0</v>
       </c>
       <c r="F94" s="0">
-        <v>0.12007422770440032</v>
+        <v>0</v>
       </c>
       <c r="G94" s="0">
-        <v>0.10058338362502617</v>
+        <v>0</v>
       </c>
       <c r="H94" s="0">
-        <v>0.090893597682214181</v>
+        <v>0</v>
       </c>
       <c r="I94" s="0">
-        <v>0.045679331095708597</v>
+        <v>0</v>
       </c>
       <c r="J94" s="0">
-        <v>0.22083179977917047</v>
+        <v>0</v>
       </c>
       <c r="K94" s="0">
-        <v>0.51546391752577847</v>
+        <v>0.12886597938144462</v>
       </c>
       <c r="L94" s="0">
-        <v>0.083973501695021546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.12552919169045967</v>
+        <v>0</v>
       </c>
       <c r="B95" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C95" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0</v>
       </c>
       <c r="D95" s="0">
-        <v>0.028851008583175027</v>
+        <v>0</v>
       </c>
       <c r="E95" s="0">
-        <v>0.019690324890360673</v>
+        <v>0</v>
       </c>
       <c r="F95" s="0">
-        <v>0.072772259214787263</v>
+        <v>0</v>
       </c>
       <c r="G95" s="0">
-        <v>0.10058338362502504</v>
+        <v>0</v>
       </c>
       <c r="H95" s="0">
-        <v>0.10793614724762815</v>
+        <v>0</v>
       </c>
       <c r="I95" s="0">
-        <v>0.031776925979623019</v>
+        <v>0</v>
       </c>
       <c r="J95" s="0">
-        <v>0.11041589988958402</v>
+        <v>0</v>
       </c>
       <c r="K95" s="0">
-        <v>1.2886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L95" s="0">
-        <v>0.054427269617142983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.063995274195136301</v>
+        <v>0</v>
       </c>
       <c r="B96" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C96" s="0">
-        <v>0.0076085164660977117</v>
+        <v>0</v>
       </c>
       <c r="D96" s="0">
-        <v>0.014425504291587513</v>
+        <v>0</v>
       </c>
       <c r="E96" s="0">
-        <v>0.014916912795727783</v>
+        <v>0</v>
       </c>
       <c r="F96" s="0">
-        <v>0.072772259214787263</v>
+        <v>0</v>
       </c>
       <c r="G96" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H96" s="0">
-        <v>0.05680849855138323</v>
+        <v>0</v>
       </c>
       <c r="I96" s="0">
-        <v>0.019860578737264385</v>
+        <v>0</v>
       </c>
       <c r="J96" s="0">
-        <v>0.092013249907986677</v>
+        <v>0</v>
       </c>
       <c r="K96" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0.052872204770938902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.034458993797381085</v>
+        <v>0</v>
       </c>
       <c r="B97" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C97" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0</v>
       </c>
       <c r="D97" s="0">
-        <v>0.014425504291587513</v>
+        <v>0</v>
       </c>
       <c r="E97" s="0">
-        <v>0.010740177212924003</v>
+        <v>0</v>
       </c>
       <c r="F97" s="0">
-        <v>0.032747516646654262</v>
+        <v>0</v>
       </c>
       <c r="G97" s="0">
-        <v>0.060350030175015036</v>
+        <v>0</v>
       </c>
       <c r="H97" s="0">
-        <v>0.045446798841106584</v>
+        <v>0</v>
       </c>
       <c r="I97" s="0">
-        <v>0.01390240511608507</v>
+        <v>0</v>
       </c>
       <c r="J97" s="0">
-        <v>0.092013249907986677</v>
+        <v>0</v>
       </c>
       <c r="K97" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L97" s="0">
-        <v>0.035766491462693964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.046765777296445758</v>
+        <v>0</v>
       </c>
       <c r="B98" s="0">
         <v>0</v>
@@ -3767,107 +3768,107 @@
         <v>0</v>
       </c>
       <c r="D98" s="0">
-        <v>0.004808501430529172</v>
+        <v>0</v>
       </c>
       <c r="E98" s="0">
-        <v>0.0053700886064620016</v>
+        <v>0</v>
       </c>
       <c r="F98" s="0">
-        <v>0.01455445184295745</v>
+        <v>0</v>
       </c>
       <c r="G98" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H98" s="0">
-        <v>0.028404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I98" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0</v>
       </c>
       <c r="J98" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K98" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L98" s="0">
-        <v>0.024881037539265367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.027074923697942281</v>
+        <v>0</v>
       </c>
       <c r="B99" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C99" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D99" s="0">
         <v>0</v>
       </c>
       <c r="E99" s="0">
-        <v>0.001790029535487334</v>
+        <v>0</v>
       </c>
       <c r="F99" s="0">
-        <v>0.016373758323327131</v>
+        <v>0</v>
       </c>
       <c r="G99" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H99" s="0">
-        <v>0.034085099130829945</v>
+        <v>0</v>
       </c>
       <c r="I99" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0</v>
       </c>
       <c r="J99" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K99" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L99" s="0">
-        <v>0.02021584300065311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.046765777296445758</v>
+        <v>0</v>
       </c>
       <c r="B100" s="0">
-        <v>0.43859649122806976</v>
+        <v>0</v>
       </c>
       <c r="C100" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D100" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E100" s="0">
-        <v>0.0047734120946328904</v>
+        <v>0</v>
       </c>
       <c r="F100" s="0">
-        <v>0.01455445184295745</v>
+        <v>0</v>
       </c>
       <c r="G100" s="0">
-        <v>0.080466706900020044</v>
+        <v>0</v>
       </c>
       <c r="H100" s="0">
-        <v>0.028404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I100" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0</v>
       </c>
       <c r="J100" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K100" s="0">
-        <v>3.479381443298966</v>
+        <v>0</v>
       </c>
       <c r="L100" s="0">
-        <v>0.021770907846857195</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
